--- a/2.RD_CGE/Input_w-t/240125_Projection.xlsx
+++ b/2.RD_CGE/Input_w-t/240125_Projection.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DD8FDD-6B85-44AD-AF7F-EB62C4056D34}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A53B6FE-DB38-499B-B142-389F4F82851C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="699" activeTab="2" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="699" activeTab="9" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -19,7 +19,10 @@
     <sheet name="GDP_Projection" sheetId="3" r:id="rId4"/>
     <sheet name="TOT_POP_Projection" sheetId="5" r:id="rId5"/>
     <sheet name="AEEI" sheetId="11" r:id="rId6"/>
-    <sheet name="CTAX" sheetId="13" r:id="rId7"/>
+    <sheet name="CTAX_145" sheetId="13" r:id="rId7"/>
+    <sheet name="CTAX_285" sheetId="14" r:id="rId8"/>
+    <sheet name="CTAX_425" sheetId="15" r:id="rId9"/>
+    <sheet name="CTAX_565" sheetId="16" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GDP_Projection!$A$1:$CF$18</definedName>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="43">
   <si>
     <t>01_KOR</t>
   </si>
@@ -1979,6 +1982,2308 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B12D2D-5736-4639-9315-A9C245758862}">
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="1">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="1">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F2" s="15">
+        <f>E2+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="15">
+        <f t="shared" ref="G2:AG2" si="0">F2+0.2</f>
+        <v>0.45</v>
+      </c>
+      <c r="H2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="I2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.05</v>
+      </c>
+      <c r="K2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="L2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.45</v>
+      </c>
+      <c r="M2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.65</v>
+      </c>
+      <c r="N2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD2" s="15">
+        <f t="shared" si="0"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE2" s="15">
+        <f t="shared" si="0"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF2" s="15">
+        <f t="shared" si="0"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG2" s="15">
+        <f t="shared" si="0"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="15">
+        <f t="shared" ref="F3:AG3" si="1">E3+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="H3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.05</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="L3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.45</v>
+      </c>
+      <c r="M3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.65</v>
+      </c>
+      <c r="N3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T3" s="15">
+        <f t="shared" si="1"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U3" s="15">
+        <f t="shared" si="1"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V3" s="15">
+        <f t="shared" si="1"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W3" s="15">
+        <f t="shared" si="1"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X3" s="15">
+        <f t="shared" si="1"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y3" s="15">
+        <f t="shared" si="1"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z3" s="15">
+        <f t="shared" si="1"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA3" s="15">
+        <f t="shared" si="1"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB3" s="15">
+        <f t="shared" si="1"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC3" s="15">
+        <f t="shared" si="1"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD3" s="15">
+        <f t="shared" si="1"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE3" s="15">
+        <f t="shared" si="1"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF3" s="15">
+        <f t="shared" si="1"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG3" s="15">
+        <f t="shared" si="1"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" ref="F4:AG4" si="2">E4+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.05</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="L4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.45</v>
+      </c>
+      <c r="M4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.65</v>
+      </c>
+      <c r="N4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T4" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U4" s="15">
+        <f t="shared" si="2"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V4" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W4" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X4" s="15">
+        <f t="shared" si="2"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y4" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z4" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA4" s="15">
+        <f t="shared" si="2"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB4" s="15">
+        <f t="shared" si="2"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC4" s="15">
+        <f t="shared" si="2"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD4" s="15">
+        <f t="shared" si="2"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE4" s="15">
+        <f t="shared" si="2"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF4" s="15">
+        <f t="shared" si="2"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG4" s="15">
+        <f t="shared" si="2"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" ref="F5:AG5" si="3">E5+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="H5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.05</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.25</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.45</v>
+      </c>
+      <c r="M5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.65</v>
+      </c>
+      <c r="N5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="3"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U5" s="15">
+        <f t="shared" si="3"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V5" s="15">
+        <f t="shared" si="3"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W5" s="15">
+        <f t="shared" si="3"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X5" s="15">
+        <f t="shared" si="3"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y5" s="15">
+        <f t="shared" si="3"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z5" s="15">
+        <f t="shared" si="3"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA5" s="15">
+        <f t="shared" si="3"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB5" s="15">
+        <f t="shared" si="3"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC5" s="15">
+        <f t="shared" si="3"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD5" s="15">
+        <f t="shared" si="3"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE5" s="15">
+        <f t="shared" si="3"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF5" s="15">
+        <f t="shared" si="3"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG5" s="15">
+        <f t="shared" si="3"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" ref="F6:AG6" si="4">E6+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.45</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.65</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.05</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.25</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.45</v>
+      </c>
+      <c r="M6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.65</v>
+      </c>
+      <c r="N6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="4"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U6" s="15">
+        <f t="shared" si="4"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V6" s="15">
+        <f t="shared" si="4"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W6" s="15">
+        <f t="shared" si="4"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X6" s="15">
+        <f t="shared" si="4"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y6" s="15">
+        <f t="shared" si="4"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z6" s="15">
+        <f t="shared" si="4"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA6" s="15">
+        <f t="shared" si="4"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB6" s="15">
+        <f t="shared" si="4"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC6" s="15">
+        <f t="shared" si="4"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD6" s="15">
+        <f t="shared" si="4"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE6" s="15">
+        <f t="shared" si="4"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF6" s="15">
+        <f t="shared" si="4"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG6" s="15">
+        <f t="shared" si="4"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" ref="F7:AG7" si="5">E7+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.45</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.05</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.45</v>
+      </c>
+      <c r="M7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.65</v>
+      </c>
+      <c r="N7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T7" s="15">
+        <f t="shared" si="5"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U7" s="15">
+        <f t="shared" si="5"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V7" s="15">
+        <f t="shared" si="5"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W7" s="15">
+        <f t="shared" si="5"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X7" s="15">
+        <f t="shared" si="5"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y7" s="15">
+        <f t="shared" si="5"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z7" s="15">
+        <f t="shared" si="5"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA7" s="15">
+        <f t="shared" si="5"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB7" s="15">
+        <f t="shared" si="5"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC7" s="15">
+        <f t="shared" si="5"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD7" s="15">
+        <f t="shared" si="5"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE7" s="15">
+        <f t="shared" si="5"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF7" s="15">
+        <f t="shared" si="5"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG7" s="15">
+        <f t="shared" si="5"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" ref="F8:AG8" si="6">E8+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.45</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.65</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.05</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.25</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.45</v>
+      </c>
+      <c r="M8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.65</v>
+      </c>
+      <c r="N8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" si="6"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U8" s="15">
+        <f t="shared" si="6"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V8" s="15">
+        <f t="shared" si="6"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" si="6"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X8" s="15">
+        <f t="shared" si="6"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y8" s="15">
+        <f t="shared" si="6"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z8" s="15">
+        <f t="shared" si="6"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA8" s="15">
+        <f t="shared" si="6"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB8" s="15">
+        <f t="shared" si="6"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC8" s="15">
+        <f t="shared" si="6"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD8" s="15">
+        <f t="shared" si="6"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE8" s="15">
+        <f t="shared" si="6"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF8" s="15">
+        <f t="shared" si="6"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG8" s="15">
+        <f t="shared" si="6"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" ref="F9:AG9" si="7">E9+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.45</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.65</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.05</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.25</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.45</v>
+      </c>
+      <c r="M9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.65</v>
+      </c>
+      <c r="N9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T9" s="15">
+        <f t="shared" si="7"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U9" s="15">
+        <f t="shared" si="7"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V9" s="15">
+        <f t="shared" si="7"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W9" s="15">
+        <f t="shared" si="7"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X9" s="15">
+        <f t="shared" si="7"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y9" s="15">
+        <f t="shared" si="7"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z9" s="15">
+        <f t="shared" si="7"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA9" s="15">
+        <f t="shared" si="7"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB9" s="15">
+        <f t="shared" si="7"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC9" s="15">
+        <f t="shared" si="7"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD9" s="15">
+        <f t="shared" si="7"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE9" s="15">
+        <f t="shared" si="7"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF9" s="15">
+        <f t="shared" si="7"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG9" s="15">
+        <f t="shared" si="7"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" ref="F10:AG10" si="8">E10+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.45</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.05</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.25</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.45</v>
+      </c>
+      <c r="M10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.65</v>
+      </c>
+      <c r="N10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T10" s="15">
+        <f t="shared" si="8"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U10" s="15">
+        <f t="shared" si="8"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V10" s="15">
+        <f t="shared" si="8"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W10" s="15">
+        <f t="shared" si="8"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X10" s="15">
+        <f t="shared" si="8"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" si="8"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z10" s="15">
+        <f t="shared" si="8"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA10" s="15">
+        <f t="shared" si="8"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB10" s="15">
+        <f t="shared" si="8"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC10" s="15">
+        <f t="shared" si="8"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD10" s="15">
+        <f t="shared" si="8"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE10" s="15">
+        <f t="shared" si="8"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF10" s="15">
+        <f t="shared" si="8"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG10" s="15">
+        <f t="shared" si="8"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" ref="F11:AG11" si="9">E11+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.45</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.65</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.05</v>
+      </c>
+      <c r="K11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.25</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.45</v>
+      </c>
+      <c r="M11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.65</v>
+      </c>
+      <c r="N11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="9"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U11" s="15">
+        <f t="shared" si="9"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V11" s="15">
+        <f t="shared" si="9"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W11" s="15">
+        <f t="shared" si="9"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X11" s="15">
+        <f t="shared" si="9"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y11" s="15">
+        <f t="shared" si="9"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z11" s="15">
+        <f t="shared" si="9"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA11" s="15">
+        <f t="shared" si="9"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB11" s="15">
+        <f t="shared" si="9"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC11" s="15">
+        <f t="shared" si="9"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD11" s="15">
+        <f t="shared" si="9"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE11" s="15">
+        <f t="shared" si="9"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF11" s="15">
+        <f t="shared" si="9"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG11" s="15">
+        <f t="shared" si="9"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" ref="F12:AG12" si="10">E12+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.45</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.65</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.05</v>
+      </c>
+      <c r="K12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.25</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.45</v>
+      </c>
+      <c r="M12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.65</v>
+      </c>
+      <c r="N12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T12" s="15">
+        <f t="shared" si="10"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U12" s="15">
+        <f t="shared" si="10"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="10"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W12" s="15">
+        <f t="shared" si="10"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X12" s="15">
+        <f t="shared" si="10"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y12" s="15">
+        <f t="shared" si="10"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z12" s="15">
+        <f t="shared" si="10"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA12" s="15">
+        <f t="shared" si="10"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB12" s="15">
+        <f t="shared" si="10"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC12" s="15">
+        <f t="shared" si="10"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD12" s="15">
+        <f t="shared" si="10"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE12" s="15">
+        <f t="shared" si="10"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF12" s="15">
+        <f t="shared" si="10"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG12" s="15">
+        <f t="shared" si="10"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" ref="F13:AG13" si="11">E13+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.45</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.65</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.05</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.25</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.45</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.65</v>
+      </c>
+      <c r="N13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T13" s="15">
+        <f t="shared" si="11"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U13" s="15">
+        <f t="shared" si="11"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="11"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W13" s="15">
+        <f t="shared" si="11"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X13" s="15">
+        <f t="shared" si="11"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y13" s="15">
+        <f t="shared" si="11"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z13" s="15">
+        <f t="shared" si="11"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA13" s="15">
+        <f t="shared" si="11"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB13" s="15">
+        <f t="shared" si="11"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC13" s="15">
+        <f t="shared" si="11"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD13" s="15">
+        <f t="shared" si="11"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE13" s="15">
+        <f t="shared" si="11"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF13" s="15">
+        <f t="shared" si="11"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG13" s="15">
+        <f t="shared" si="11"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" ref="F14:AG14" si="12">E14+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.45</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.65</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.05</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.25</v>
+      </c>
+      <c r="L14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.45</v>
+      </c>
+      <c r="M14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.65</v>
+      </c>
+      <c r="N14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T14" s="15">
+        <f t="shared" si="12"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U14" s="15">
+        <f t="shared" si="12"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="12"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W14" s="15">
+        <f t="shared" si="12"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X14" s="15">
+        <f t="shared" si="12"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y14" s="15">
+        <f t="shared" si="12"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z14" s="15">
+        <f t="shared" si="12"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA14" s="15">
+        <f t="shared" si="12"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB14" s="15">
+        <f t="shared" si="12"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC14" s="15">
+        <f t="shared" si="12"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD14" s="15">
+        <f t="shared" si="12"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE14" s="15">
+        <f t="shared" si="12"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF14" s="15">
+        <f t="shared" si="12"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG14" s="15">
+        <f t="shared" si="12"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" ref="F15:AG15" si="13">E15+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.45</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.65</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.05</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.25</v>
+      </c>
+      <c r="L15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.45</v>
+      </c>
+      <c r="M15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.65</v>
+      </c>
+      <c r="N15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T15" s="15">
+        <f t="shared" si="13"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U15" s="15">
+        <f t="shared" si="13"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V15" s="15">
+        <f t="shared" si="13"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W15" s="15">
+        <f t="shared" si="13"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X15" s="15">
+        <f t="shared" si="13"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y15" s="15">
+        <f t="shared" si="13"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z15" s="15">
+        <f t="shared" si="13"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA15" s="15">
+        <f t="shared" si="13"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB15" s="15">
+        <f t="shared" si="13"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC15" s="15">
+        <f t="shared" si="13"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD15" s="15">
+        <f t="shared" si="13"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE15" s="15">
+        <f t="shared" si="13"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF15" s="15">
+        <f t="shared" si="13"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG15" s="15">
+        <f t="shared" si="13"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" ref="F16:AG16" si="14">E16+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.45</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.65</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.05</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.25</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.45</v>
+      </c>
+      <c r="M16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.65</v>
+      </c>
+      <c r="N16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T16" s="15">
+        <f t="shared" si="14"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U16" s="15">
+        <f t="shared" si="14"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" si="14"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W16" s="15">
+        <f t="shared" si="14"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X16" s="15">
+        <f t="shared" si="14"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y16" s="15">
+        <f t="shared" si="14"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z16" s="15">
+        <f t="shared" si="14"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA16" s="15">
+        <f t="shared" si="14"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB16" s="15">
+        <f t="shared" si="14"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC16" s="15">
+        <f t="shared" si="14"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD16" s="15">
+        <f t="shared" si="14"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE16" s="15">
+        <f t="shared" si="14"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF16" s="15">
+        <f t="shared" si="14"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG16" s="15">
+        <f t="shared" si="14"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="15">
+        <f t="shared" ref="F17:AG17" si="15">E17+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.45</v>
+      </c>
+      <c r="H17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.65</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.05</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.25</v>
+      </c>
+      <c r="L17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.45</v>
+      </c>
+      <c r="M17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.65</v>
+      </c>
+      <c r="N17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T17" s="15">
+        <f t="shared" si="15"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U17" s="15">
+        <f t="shared" si="15"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="15"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W17" s="15">
+        <f t="shared" si="15"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X17" s="15">
+        <f t="shared" si="15"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y17" s="15">
+        <f t="shared" si="15"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z17" s="15">
+        <f t="shared" si="15"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA17" s="15">
+        <f t="shared" si="15"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB17" s="15">
+        <f t="shared" si="15"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC17" s="15">
+        <f t="shared" si="15"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD17" s="15">
+        <f t="shared" si="15"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE17" s="15">
+        <f t="shared" si="15"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF17" s="15">
+        <f t="shared" si="15"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG17" s="15">
+        <f t="shared" si="15"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" ref="F18:AG18" si="16">E18+0.2</f>
+        <v>0.25</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.45</v>
+      </c>
+      <c r="H18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.65</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.05</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.25</v>
+      </c>
+      <c r="L18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.45</v>
+      </c>
+      <c r="M18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.65</v>
+      </c>
+      <c r="N18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.8499999999999999</v>
+      </c>
+      <c r="O18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="P18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="R18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.6500000000000004</v>
+      </c>
+      <c r="S18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.8500000000000005</v>
+      </c>
+      <c r="T18" s="15">
+        <f t="shared" si="16"/>
+        <v>3.0500000000000007</v>
+      </c>
+      <c r="U18" s="15">
+        <f t="shared" si="16"/>
+        <v>3.2500000000000009</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="16"/>
+        <v>3.4500000000000011</v>
+      </c>
+      <c r="W18" s="15">
+        <f t="shared" si="16"/>
+        <v>3.6500000000000012</v>
+      </c>
+      <c r="X18" s="15">
+        <f t="shared" si="16"/>
+        <v>3.8500000000000014</v>
+      </c>
+      <c r="Y18" s="15">
+        <f t="shared" si="16"/>
+        <v>4.0500000000000016</v>
+      </c>
+      <c r="Z18" s="15">
+        <f t="shared" si="16"/>
+        <v>4.2500000000000018</v>
+      </c>
+      <c r="AA18" s="15">
+        <f t="shared" si="16"/>
+        <v>4.450000000000002</v>
+      </c>
+      <c r="AB18" s="15">
+        <f t="shared" si="16"/>
+        <v>4.6500000000000021</v>
+      </c>
+      <c r="AC18" s="15">
+        <f t="shared" si="16"/>
+        <v>4.8500000000000023</v>
+      </c>
+      <c r="AD18" s="15">
+        <f t="shared" si="16"/>
+        <v>5.0500000000000025</v>
+      </c>
+      <c r="AE18" s="15">
+        <f t="shared" si="16"/>
+        <v>5.2500000000000027</v>
+      </c>
+      <c r="AF18" s="15">
+        <f t="shared" si="16"/>
+        <v>5.4500000000000028</v>
+      </c>
+      <c r="AG18" s="15">
+        <f t="shared" si="16"/>
+        <v>5.650000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D8B7BF9-68EF-4E22-96B6-AD75678CC8E4}">
   <dimension ref="A1:R84"/>
@@ -25341,115 +27646,115 @@
         <v>0.05</v>
       </c>
       <c r="F2" s="15">
-        <f t="shared" ref="F2:F18" si="0">E2+0.05</f>
+        <f>E2+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G2" s="15">
-        <f t="shared" ref="G2:AG2" si="1">F2+0.05</f>
+        <f t="shared" ref="G2:AG2" si="0">F2+0.05</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="H2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="I2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="J2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="K2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
       <c r="L2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="Q2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
       <c r="R2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG2" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -25470,115 +27775,115 @@
         <v>0.05</v>
       </c>
       <c r="F3" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F3:AG3" si="1">E3+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G3" s="15">
-        <f t="shared" ref="G3:G18" si="2">F3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H3" s="15">
-        <f t="shared" ref="H3:H18" si="3">G3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
       <c r="I3" s="15">
-        <f t="shared" ref="I3:I18" si="4">H3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
       <c r="J3" s="15">
-        <f t="shared" ref="J3:J18" si="5">I3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
       <c r="K3" s="15">
-        <f t="shared" ref="K3:K18" si="6">J3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
       <c r="L3" s="15">
-        <f t="shared" ref="L3:L18" si="7">K3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M3" s="15">
-        <f t="shared" ref="M3:M18" si="8">L3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N3" s="15">
-        <f t="shared" ref="N3:N18" si="9">M3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O3" s="15">
-        <f t="shared" ref="O3:O18" si="10">N3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P3" s="15">
-        <f t="shared" ref="P3:P18" si="11">O3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="Q3" s="15">
-        <f t="shared" ref="Q3:Q18" si="12">P3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
       <c r="R3" s="15">
-        <f t="shared" ref="R3:R18" si="13">Q3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S3" s="15">
-        <f t="shared" ref="S3:S18" si="14">R3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T3" s="15">
-        <f t="shared" ref="T3:T18" si="15">S3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U3" s="15">
-        <f t="shared" ref="U3:U18" si="16">T3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V3" s="15">
-        <f t="shared" ref="V3:V18" si="17">U3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W3" s="15">
-        <f t="shared" ref="W3:W18" si="18">V3+0.05</f>
+        <f t="shared" si="1"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X3" s="15">
-        <f t="shared" ref="X3:X18" si="19">W3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y3" s="15">
-        <f t="shared" ref="Y3:Y18" si="20">X3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z3" s="15">
-        <f t="shared" ref="Z3:Z18" si="21">Y3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA3" s="15">
-        <f t="shared" ref="AA3:AA18" si="22">Z3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB3" s="15">
-        <f t="shared" ref="AB3:AB18" si="23">AA3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC3" s="15">
-        <f t="shared" ref="AC3:AC18" si="24">AB3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD3" s="15">
-        <f t="shared" ref="AD3:AD18" si="25">AC3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE3" s="15">
-        <f t="shared" ref="AE3:AE18" si="26">AD3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF3" s="15">
-        <f t="shared" ref="AF3:AF18" si="27">AE3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG3" s="15">
-        <f t="shared" ref="AG3:AG18" si="28">AF3+0.05</f>
+        <f t="shared" si="1"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -25599,7 +27904,7 @@
         <v>0.05</v>
       </c>
       <c r="F4" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F4:AG4" si="2">E4+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G4" s="15">
@@ -25607,107 +27912,107 @@
         <v>0.15000000000000002</v>
       </c>
       <c r="H4" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="I4" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="J4" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="K4" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0.35</v>
       </c>
       <c r="L4" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M4" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N4" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O4" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P4" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="Q4" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="2"/>
         <v>0.65</v>
       </c>
       <c r="R4" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S4" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="2"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T4" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="2"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U4" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V4" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W4" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X4" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="2"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y4" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="2"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z4" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA4" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="2"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB4" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="2"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC4" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="2"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD4" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="2"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE4" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="2"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF4" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG4" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="2"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -25728,11 +28033,11 @@
         <v>0.05</v>
       </c>
       <c r="F5" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F5:AG5" si="3">E5+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G5" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H5" s="15">
@@ -25740,103 +28045,103 @@
         <v>0.2</v>
       </c>
       <c r="I5" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="J5" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
       <c r="K5" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
       <c r="L5" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M5" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N5" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O5" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="3"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P5" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="Q5" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="R5" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S5" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="3"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T5" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="3"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U5" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="3"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V5" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W5" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="3"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X5" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y5" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="3"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z5" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="3"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA5" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="3"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB5" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="3"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC5" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="3"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD5" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="3"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE5" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="3"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF5" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="3"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG5" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="3"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -25857,15 +28162,15 @@
         <v>0.05</v>
       </c>
       <c r="F6" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F6:AG6" si="4">E6+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G6" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H6" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="I6" s="15">
@@ -25873,99 +28178,99 @@
         <v>0.25</v>
       </c>
       <c r="J6" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
       <c r="K6" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0.35</v>
       </c>
       <c r="L6" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M6" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N6" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O6" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="4"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P6" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
       <c r="Q6" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="R6" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="4"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S6" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T6" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="4"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U6" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="4"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V6" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="4"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W6" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="4"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X6" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="4"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y6" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="4"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z6" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="4"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA6" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB6" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="4"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC6" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="4"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD6" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="4"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE6" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="4"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF6" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="4"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG6" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="4"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -25986,19 +28291,19 @@
         <v>0.05</v>
       </c>
       <c r="F7" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F7:AG7" si="5">E7+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H7" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="J7" s="15">
@@ -26006,95 +28311,95 @@
         <v>0.3</v>
       </c>
       <c r="K7" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.35</v>
       </c>
       <c r="L7" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M7" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N7" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O7" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P7" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
       <c r="Q7" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>0.65</v>
       </c>
       <c r="R7" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S7" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="5"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T7" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U7" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V7" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="5"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W7" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="5"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X7" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="5"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y7" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="5"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z7" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="5"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA7" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="5"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB7" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC7" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="5"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD7" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="5"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE7" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="5"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF7" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="5"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG7" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="5"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26115,23 +28420,23 @@
         <v>0.05</v>
       </c>
       <c r="F8" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F8:AG8" si="6">E8+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G8" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H8" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="K8" s="15">
@@ -26139,91 +28444,91 @@
         <v>0.35</v>
       </c>
       <c r="L8" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N8" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O8" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P8" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
       <c r="Q8" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0.65</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S8" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T8" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V8" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W8" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="6"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X8" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="6"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y8" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="6"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z8" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA8" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="6"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB8" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="6"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC8" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD8" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="6"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE8" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="6"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF8" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="6"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG8" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="6"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26244,27 +28549,27 @@
         <v>0.05</v>
       </c>
       <c r="F9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F9:AG9" si="7">E9+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G9" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H9" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="K9" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.35</v>
       </c>
       <c r="L9" s="15">
@@ -26272,87 +28577,87 @@
         <v>0.39999999999999997</v>
       </c>
       <c r="M9" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N9" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O9" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P9" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="Q9" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>0.65</v>
       </c>
       <c r="R9" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="7"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S9" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T9" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U9" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="7"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W9" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X9" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y9" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z9" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA9" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB9" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC9" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD9" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE9" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="7"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF9" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="7"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG9" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="7"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26373,31 +28678,31 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F10:AG10" si="8">E10+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G10" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H10" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>0.2</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0.3</v>
       </c>
       <c r="K10" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="L10" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M10" s="15">
@@ -26405,83 +28710,83 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="N10" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O10" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P10" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0.6</v>
       </c>
       <c r="Q10" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0.65</v>
       </c>
       <c r="R10" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S10" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="8"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T10" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="8"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U10" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="8"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V10" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="8"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W10" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X10" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="8"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y10" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="8"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z10" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="8"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA10" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="8"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB10" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="8"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC10" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="8"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD10" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="8"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE10" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF10" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG10" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26502,35 +28807,35 @@
         <v>0.05</v>
       </c>
       <c r="F11" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F11:AG11" si="9">E11+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G11" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H11" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
       <c r="K11" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
       <c r="L11" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M11" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N11" s="15">
@@ -26538,79 +28843,79 @@
         <v>0.49999999999999994</v>
       </c>
       <c r="O11" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P11" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
       <c r="Q11" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0.65</v>
       </c>
       <c r="R11" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S11" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T11" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="9"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U11" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="9"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V11" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W11" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="9"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X11" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y11" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="9"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z11" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="9"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA11" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="9"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB11" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="9"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC11" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="9"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD11" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="9"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE11" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="9"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF11" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="9"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG11" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="9"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26631,39 +28936,39 @@
         <v>0.05</v>
       </c>
       <c r="F12" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F12:AG12" si="10">E12+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G12" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="10"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H12" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="K12" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="L12" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M12" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N12" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O12" s="15">
@@ -26671,75 +28976,75 @@
         <v>0.54999999999999993</v>
       </c>
       <c r="P12" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
       <c r="Q12" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.65</v>
       </c>
       <c r="R12" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S12" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T12" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U12" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="10"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V12" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="10"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W12" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X12" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="10"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y12" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z12" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="10"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA12" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="10"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB12" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="10"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC12" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="10"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD12" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="10"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE12" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="10"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF12" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="10"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG12" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="10"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26760,43 +29065,43 @@
         <v>0.05</v>
       </c>
       <c r="F13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F13:AG13" si="11">E13+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G13" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H13" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>0.3</v>
       </c>
       <c r="K13" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0.35</v>
       </c>
       <c r="L13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M13" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N13" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O13" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P13" s="15">
@@ -26804,71 +29109,71 @@
         <v>0.6</v>
       </c>
       <c r="Q13" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.65</v>
       </c>
       <c r="R13" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S13" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T13" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U13" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V13" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="11"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W13" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="11"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X13" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y13" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="11"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z13" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA13" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="11"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB13" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="11"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC13" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="11"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD13" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="11"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE13" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="11"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF13" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="11"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG13" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="11"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -26889,47 +29194,47 @@
         <v>0.05</v>
       </c>
       <c r="F14" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F14:AG14" si="12">E14+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G14" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H14" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>0.25</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0.3</v>
       </c>
       <c r="K14" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.35</v>
       </c>
       <c r="L14" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M14" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N14" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O14" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P14" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.6</v>
       </c>
       <c r="Q14" s="15">
@@ -26937,67 +29242,67 @@
         <v>0.65</v>
       </c>
       <c r="R14" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S14" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T14" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U14" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V14" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W14" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="12"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X14" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="12"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y14" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z14" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="12"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA14" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="12"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB14" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="12"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC14" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD14" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="12"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE14" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="12"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF14" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG14" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="12"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -27018,51 +29323,51 @@
         <v>0.05</v>
       </c>
       <c r="F15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F15:AG15" si="13">E15+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G15" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="13"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H15" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="13"/>
         <v>0.2</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>0.25</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v>0.3</v>
       </c>
       <c r="K15" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0.35</v>
       </c>
       <c r="L15" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M15" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N15" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O15" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P15" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.6</v>
       </c>
       <c r="Q15" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.65</v>
       </c>
       <c r="R15" s="15">
@@ -27070,63 +29375,63 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="S15" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T15" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U15" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V15" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W15" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X15" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="13"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y15" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z15" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA15" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="13"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB15" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="13"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC15" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="13"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD15" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="13"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE15" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="13"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF15" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="13"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG15" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="13"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -27147,55 +29452,55 @@
         <v>0.05</v>
       </c>
       <c r="F16" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F16:AG16" si="14">E16+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G16" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H16" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>0.25</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>0.3</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v>0.35</v>
       </c>
       <c r="L16" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M16" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N16" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O16" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P16" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.6</v>
       </c>
       <c r="Q16" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.65</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S16" s="15">
@@ -27203,59 +29508,59 @@
         <v>0.75000000000000011</v>
       </c>
       <c r="T16" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U16" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W16" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="14"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X16" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y16" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="14"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z16" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA16" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="14"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB16" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="14"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC16" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="14"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD16" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="14"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE16" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF16" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="14"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG16" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -27276,59 +29581,59 @@
         <v>0.05</v>
       </c>
       <c r="F17" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F17:AG17" si="15">E17+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G17" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="15"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H17" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="15"/>
         <v>0.25</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="15"/>
         <v>0.3</v>
       </c>
       <c r="K17" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>0.35</v>
       </c>
       <c r="L17" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M17" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N17" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O17" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P17" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.6</v>
       </c>
       <c r="Q17" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="R17" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S17" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T17" s="15">
@@ -27336,55 +29641,55 @@
         <v>0.80000000000000016</v>
       </c>
       <c r="U17" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.8500000000000002</v>
       </c>
       <c r="V17" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W17" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X17" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="15"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y17" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z17" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="15"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA17" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="15"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB17" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="15"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC17" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="15"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD17" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="15"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE17" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="15"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF17" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="15"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG17" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="15"/>
         <v>1.4500000000000006</v>
       </c>
     </row>
@@ -27405,63 +29710,63 @@
         <v>0.05</v>
       </c>
       <c r="F18" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F18:AG18" si="16">E18+0.05</f>
         <v>0.1</v>
       </c>
       <c r="G18" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="16"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="H18" s="15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="16"/>
         <v>0.2</v>
       </c>
       <c r="I18" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="16"/>
         <v>0.25</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
       <c r="K18" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0.35</v>
       </c>
       <c r="L18" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0.39999999999999997</v>
       </c>
       <c r="M18" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="N18" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="O18" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0.54999999999999993</v>
       </c>
       <c r="P18" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="Q18" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>0.65</v>
       </c>
       <c r="R18" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.75000000000000011</v>
       </c>
       <c r="T18" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.80000000000000016</v>
       </c>
       <c r="U18" s="15">
@@ -27469,52 +29774,4656 @@
         <v>0.8500000000000002</v>
       </c>
       <c r="V18" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0.90000000000000024</v>
       </c>
       <c r="W18" s="15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0.95000000000000029</v>
       </c>
       <c r="X18" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Y18" s="15">
-        <f t="shared" si="20"/>
+        <f t="shared" si="16"/>
         <v>1.0500000000000003</v>
       </c>
       <c r="Z18" s="15">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>1.1000000000000003</v>
       </c>
       <c r="AA18" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>1.1500000000000004</v>
       </c>
       <c r="AB18" s="15">
-        <f t="shared" si="23"/>
+        <f t="shared" si="16"/>
         <v>1.2000000000000004</v>
       </c>
       <c r="AC18" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="16"/>
         <v>1.2500000000000004</v>
       </c>
       <c r="AD18" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="16"/>
         <v>1.3000000000000005</v>
       </c>
       <c r="AE18" s="15">
-        <f t="shared" si="26"/>
+        <f t="shared" si="16"/>
         <v>1.3500000000000005</v>
       </c>
       <c r="AF18" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="16"/>
         <v>1.4000000000000006</v>
       </c>
       <c r="AG18" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="16"/>
         <v>1.4500000000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F0BF70-BEB3-4C23-BA28-705EDE33B68E}">
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="1">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="1">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F2" s="15">
+        <f>E2+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G2" s="15">
+        <f t="shared" ref="G2:AG2" si="0">F2+0.1</f>
+        <v>0.25</v>
+      </c>
+      <c r="H2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="I2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="R2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.35</v>
+      </c>
+      <c r="S2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="15">
+        <f t="shared" ref="F3:AG3" si="1">E3+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="H3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="R3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.35</v>
+      </c>
+      <c r="S3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" ref="F4:AG4" si="2">E4+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N4" s="15">
+        <f t="shared" si="2"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="R4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.35</v>
+      </c>
+      <c r="S4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X4" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG4" s="15">
+        <f t="shared" si="2"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" ref="F5:AG5" si="3">E5+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="H5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.35</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.25</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.35</v>
+      </c>
+      <c r="S5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X5" s="15">
+        <f t="shared" si="3"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG5" s="15">
+        <f t="shared" si="3"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" ref="F6:AG6" si="4">E6+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.25</v>
+      </c>
+      <c r="R6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.35</v>
+      </c>
+      <c r="S6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X6" s="15">
+        <f t="shared" si="4"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG6" s="15">
+        <f t="shared" si="4"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" ref="F7:AG7" si="5">E7+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.35</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N7" s="15">
+        <f t="shared" si="5"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.25</v>
+      </c>
+      <c r="R7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.35</v>
+      </c>
+      <c r="S7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X7" s="15">
+        <f t="shared" si="5"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG7" s="15">
+        <f t="shared" si="5"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" ref="F8:AG8" si="6">E8+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.35</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.25</v>
+      </c>
+      <c r="R8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.35</v>
+      </c>
+      <c r="S8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X8" s="15">
+        <f t="shared" si="6"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG8" s="15">
+        <f t="shared" si="6"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" ref="F9:AG9" si="7">E9+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.35</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N9" s="15">
+        <f t="shared" si="7"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.25</v>
+      </c>
+      <c r="R9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.35</v>
+      </c>
+      <c r="S9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X9" s="15">
+        <f t="shared" si="7"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG9" s="15">
+        <f t="shared" si="7"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" ref="F10:AG10" si="8">E10+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.35</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N10" s="15">
+        <f t="shared" si="8"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.25</v>
+      </c>
+      <c r="R10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.35</v>
+      </c>
+      <c r="S10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X10" s="15">
+        <f t="shared" si="8"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG10" s="15">
+        <f t="shared" si="8"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" ref="F11:AG11" si="9">E11+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.35</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N11" s="15">
+        <f t="shared" si="9"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.25</v>
+      </c>
+      <c r="R11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.35</v>
+      </c>
+      <c r="S11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X11" s="15">
+        <f t="shared" si="9"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG11" s="15">
+        <f t="shared" si="9"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" ref="F12:AG12" si="10">E12+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.35</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N12" s="15">
+        <f t="shared" si="10"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.25</v>
+      </c>
+      <c r="R12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.35</v>
+      </c>
+      <c r="S12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X12" s="15">
+        <f t="shared" si="10"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG12" s="15">
+        <f t="shared" si="10"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" ref="F13:AG13" si="11">E13+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.25</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.35</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N13" s="15">
+        <f t="shared" si="11"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.25</v>
+      </c>
+      <c r="R13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.35</v>
+      </c>
+      <c r="S13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X13" s="15">
+        <f t="shared" si="11"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG13" s="15">
+        <f t="shared" si="11"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" ref="F14:AG14" si="12">E14+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.35</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N14" s="15">
+        <f t="shared" si="12"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.25</v>
+      </c>
+      <c r="R14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.35</v>
+      </c>
+      <c r="S14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X14" s="15">
+        <f t="shared" si="12"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG14" s="15">
+        <f t="shared" si="12"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" ref="F15:AG15" si="13">E15+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.25</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.35</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N15" s="15">
+        <f t="shared" si="13"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.25</v>
+      </c>
+      <c r="R15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.35</v>
+      </c>
+      <c r="S15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X15" s="15">
+        <f t="shared" si="13"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG15" s="15">
+        <f t="shared" si="13"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" ref="F16:AG16" si="14">E16+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.25</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.35</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N16" s="15">
+        <f t="shared" si="14"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.25</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.35</v>
+      </c>
+      <c r="S16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X16" s="15">
+        <f t="shared" si="14"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG16" s="15">
+        <f t="shared" si="14"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="15">
+        <f t="shared" ref="F17:AG17" si="15">E17+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.25</v>
+      </c>
+      <c r="H17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.35</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N17" s="15">
+        <f t="shared" si="15"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.25</v>
+      </c>
+      <c r="R17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.35</v>
+      </c>
+      <c r="S17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X17" s="15">
+        <f t="shared" si="15"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG17" s="15">
+        <f t="shared" si="15"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" ref="F18:AG18" si="16">E18+0.1</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="H18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.35</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="L18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.74999999999999989</v>
+      </c>
+      <c r="M18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.84999999999999987</v>
+      </c>
+      <c r="N18" s="15">
+        <f t="shared" si="16"/>
+        <v>0.94999999999999984</v>
+      </c>
+      <c r="O18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.0499999999999998</v>
+      </c>
+      <c r="P18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.25</v>
+      </c>
+      <c r="R18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.35</v>
+      </c>
+      <c r="S18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="T18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.5500000000000003</v>
+      </c>
+      <c r="U18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.6500000000000004</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.7500000000000004</v>
+      </c>
+      <c r="W18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.8500000000000005</v>
+      </c>
+      <c r="X18" s="15">
+        <f t="shared" si="16"/>
+        <v>1.9500000000000006</v>
+      </c>
+      <c r="Y18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.0500000000000007</v>
+      </c>
+      <c r="Z18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.1500000000000008</v>
+      </c>
+      <c r="AA18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.2500000000000009</v>
+      </c>
+      <c r="AB18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.350000000000001</v>
+      </c>
+      <c r="AC18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="AD18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.5500000000000012</v>
+      </c>
+      <c r="AE18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.6500000000000012</v>
+      </c>
+      <c r="AF18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.7500000000000013</v>
+      </c>
+      <c r="AG18" s="15">
+        <f t="shared" si="16"/>
+        <v>2.8500000000000014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B36736F-CC09-489B-B698-2F45B1A52627}">
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="1">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="1">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="1">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="1">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="1">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F2" s="15">
+        <f>E2+0.15</f>
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="15">
+        <f t="shared" ref="G2:AG11" si="0">F2+0.15</f>
+        <v>0.35</v>
+      </c>
+      <c r="H2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K2" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R2" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X2" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE2" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG2" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="15">
+        <f t="shared" ref="F3:U18" si="1">E3+0.15</f>
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="H3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="J3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="K3" s="15">
+        <f t="shared" si="1"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="N3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.4</v>
+      </c>
+      <c r="O3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R3" s="15">
+        <f t="shared" si="1"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V3" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W3" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X3" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE3" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF3" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG3" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K4" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE4" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF4" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG4" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S5" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U5" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V5" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W5" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X5" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE5" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF5" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG5" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X6" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE6" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF6" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG6" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R7" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S7" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T7" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U7" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V7" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W7" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X7" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE7" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF7" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG7" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R8" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S8" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U8" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V8" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X8" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE8" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF8" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG8" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R9" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S9" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T9" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U9" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V9" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W9" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X9" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE9" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF9" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG9" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R10" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S10" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T10" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U10" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V10" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W10" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X10" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE10" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF10" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG10" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="K11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="N11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="O11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R11" s="15">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S11" s="15">
+        <f t="shared" si="0"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U11" s="15">
+        <f t="shared" si="0"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V11" s="15">
+        <f t="shared" si="0"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W11" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X11" s="15">
+        <f t="shared" si="0"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE11" s="15">
+        <f t="shared" si="0"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF11" s="15">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG11" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" ref="G12:AG18" si="2">F12+0.15</f>
+        <v>0.35</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K12" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R12" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S12" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T12" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U12" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W12" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X12" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE12" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF12" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG12" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S13" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T13" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U13" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V13" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W13" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X13" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE13" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF13" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG13" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R14" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S14" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T14" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U14" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W14" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X14" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE14" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF14" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG14" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R15" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S15" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T15" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U15" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V15" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W15" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X15" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE15" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF15" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG15" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S16" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T16" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U16" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W16" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X16" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE16" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF16" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG16" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="H17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R17" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S17" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T17" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U17" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W17" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X17" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE17" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF17" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG17" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="H18" s="15">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="L18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.25</v>
+      </c>
+      <c r="N18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="O18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.5499999999999998</v>
+      </c>
+      <c r="P18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.6999999999999997</v>
+      </c>
+      <c r="Q18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.8499999999999996</v>
+      </c>
+      <c r="R18" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9999999999999996</v>
+      </c>
+      <c r="S18" s="15">
+        <f t="shared" si="2"/>
+        <v>2.1499999999999995</v>
+      </c>
+      <c r="T18" s="15">
+        <f t="shared" si="2"/>
+        <v>2.2999999999999994</v>
+      </c>
+      <c r="U18" s="15">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999993</v>
+      </c>
+      <c r="V18" s="15">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999992</v>
+      </c>
+      <c r="W18" s="15">
+        <f t="shared" si="2"/>
+        <v>2.7499999999999991</v>
+      </c>
+      <c r="X18" s="15">
+        <f t="shared" si="2"/>
+        <v>2.899999999999999</v>
+      </c>
+      <c r="Y18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.0499999999999989</v>
+      </c>
+      <c r="Z18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1999999999999988</v>
+      </c>
+      <c r="AA18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.3499999999999988</v>
+      </c>
+      <c r="AB18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.4999999999999987</v>
+      </c>
+      <c r="AC18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.6499999999999986</v>
+      </c>
+      <c r="AD18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.7999999999999985</v>
+      </c>
+      <c r="AE18" s="15">
+        <f t="shared" si="2"/>
+        <v>3.9499999999999984</v>
+      </c>
+      <c r="AF18" s="15">
+        <f t="shared" si="2"/>
+        <v>4.0999999999999988</v>
+      </c>
+      <c r="AG18" s="15">
+        <f t="shared" si="2"/>
+        <v>4.2499999999999991</v>
       </c>
     </row>
   </sheetData>
